--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_60.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_60.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>16</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
@@ -668,12 +668,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -734,10 +734,10 @@
         <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
         <v>17</v>
@@ -762,17 +762,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_45.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,17 +782,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
-        <v>9</v>
-      </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
         <v>11</v>
@@ -861,12 +861,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -960,7 +960,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1136,7 @@
         <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1235,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1328,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V9" t="n">
         <v>4</v>
@@ -1356,17 +1356,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1424,13 +1424,13 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
         <v>17</v>
@@ -1455,17 +1455,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
         <v>8</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1564,17 +1564,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1727,10 +1727,10 @@
         <v>17</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
         <v>16</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
         <v>18</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2120,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
         <v>4</v>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2168,17 +2168,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
         <v>14</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2315,7 +2315,7 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U19" t="n">
         <v>8</v>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2417,10 +2417,10 @@
         <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
         <v>7</v>
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_08.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_06.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_06.jpg</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
         <v>14</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2544,19 +2544,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_08.jpg</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_10.jpg</t>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2612,13 +2612,13 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" t="n">
         <v>9</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
       </c>
       <c r="W22" t="n">
         <v>8</v>
@@ -2643,14 +2643,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_08.jpg</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_21.jpg</t>
@@ -2658,19 +2658,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>glasses</t>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
         <v>9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>18</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,7 +2810,7 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U24" t="n">
         <v>7</v>
@@ -2819,7 +2819,7 @@
         <v>17</v>
       </c>
       <c r="W24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2918,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3017,7 +3017,7 @@
         <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>17</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>16</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
         <v>7</v>
@@ -3336,19 +3336,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_45.jpg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_26.jpg</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_41.jpg</t>
@@ -3356,17 +3356,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3404,13 +3404,13 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>9</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5</v>
       </c>
       <c r="W30" t="n">
         <v>4</v>
@@ -3435,12 +3435,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3503,10 +3503,10 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
         <v>8</v>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_26.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_40.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_40.jpg</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_34.jpg</t>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3602,13 +3602,13 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
         <v>17</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3707,7 +3707,7 @@
         <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W33" t="n">
         <v>11</v>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3806,10 +3806,10 @@
         <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3902,7 +3902,7 @@
         <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V35" t="n">
         <v>17</v>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3998,13 +3998,13 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V37" t="n">
         <v>16</v>
       </c>
       <c r="W37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,7 +4196,7 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U38" t="n">
         <v>4</v>
@@ -4205,7 +4205,7 @@
         <v>15</v>
       </c>
       <c r="W38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4301,10 +4301,10 @@
         <v>17</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4694,10 +4694,10 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W43" t="n">
         <v>16</v>
@@ -4722,12 +4722,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4790,10 +4790,10 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V44" t="n">
         <v>7</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4889,13 +4889,13 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U45" t="n">
         <v>8</v>
       </c>
       <c r="V45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
         <v>4</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4991,7 +4991,7 @@
         <v>8</v>
       </c>
       <c r="U46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
         <v>14</v>
@@ -5019,42 +5019,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_06.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_40.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_40.jpg</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5087,16 +5087,16 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
         <v>17</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -5118,19 +5118,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_08.jpg</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_14.jpg</t>
@@ -5138,17 +5138,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5186,13 +5186,13 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
+        <v>2</v>
+      </c>
+      <c r="V48" t="n">
         <v>9</v>
-      </c>
-      <c r="V48" t="n">
-        <v>5</v>
       </c>
       <c r="W48" t="n">
         <v>4</v>
@@ -5217,42 +5217,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_10.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_10.jpg</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
         <v>9</v>
-      </c>
-      <c r="U49" t="n">
-        <v>5</v>
       </c>
       <c r="V49" t="n">
         <v>1</v>
       </c>
       <c r="W49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_27.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U50" t="n">
         <v>7</v>
       </c>
       <c r="V50" t="n">
+        <v>10</v>
+      </c>
+      <c r="W50" t="n">
         <v>3</v>
-      </c>
-      <c r="W50" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5492,7 +5492,7 @@
         <v>17</v>
       </c>
       <c r="W51" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="W52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W53" t="n">
         <v>14</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>16</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W54" t="n">
         <v>11</v>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5882,10 +5882,10 @@
         <v>16</v>
       </c>
       <c r="U55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W55" t="n">
         <v>4</v>
@@ -5910,14 +5910,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_45.jpg</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_40.jpg</t>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5978,10 +5978,10 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
         <v>2</v>
-      </c>
-      <c r="U56" t="n">
-        <v>9</v>
       </c>
       <c r="V56" t="n">
         <v>1</v>
@@ -6009,19 +6009,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_26.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_26.jpg</t>
-        </is>
-      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_34.jpg</t>
@@ -6029,17 +6029,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6077,13 +6077,13 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
+      </c>
+      <c r="V57" t="n">
         <v>9</v>
-      </c>
-      <c r="U57" t="n">
-        <v>10</v>
-      </c>
-      <c r="V57" t="n">
-        <v>5</v>
       </c>
       <c r="W57" t="n">
         <v>17</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6176,7 +6176,7 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U58" t="n">
         <v>1</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6281,7 +6281,7 @@
         <v>7</v>
       </c>
       <c r="V59" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W59" t="n">
         <v>11</v>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6383,7 +6383,7 @@
         <v>11</v>
       </c>
       <c r="W60" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -6410,19 +6410,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>stimuli/house/house_03.jpg</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_13.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_13.jpg</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>hand</t>
@@ -6430,17 +6430,17 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6476,13 +6476,13 @@
         <v>8</v>
       </c>
       <c r="U61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V61" t="n">
         <v>16</v>
       </c>
       <c r="W61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_48.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U62" t="n">
+        <v>3</v>
+      </c>
+      <c r="V62" t="n">
+        <v>10</v>
+      </c>
+      <c r="W62" t="n">
         <v>6</v>
-      </c>
-      <c r="V62" t="n">
-        <v>3</v>
-      </c>
-      <c r="W62" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -6603,19 +6603,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_48.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6671,13 +6671,13 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>10</v>
+      </c>
+      <c r="V63" t="n">
         <v>6</v>
-      </c>
-      <c r="U63" t="n">
-        <v>3</v>
-      </c>
-      <c r="V63" t="n">
-        <v>2</v>
       </c>
       <c r="W63" t="n">
         <v>7</v>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,7 +6770,7 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U64" t="n">
         <v>4</v>
@@ -6779,7 +6779,7 @@
         <v>15</v>
       </c>
       <c r="W64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6878,7 +6878,7 @@
         <v>16</v>
       </c>
       <c r="W65" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>17</v>
       </c>
       <c r="V67" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W67" t="n">
         <v>16</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W68" t="n">
         <v>4</v>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7268,10 +7268,10 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
         <v>18</v>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7364,10 +7364,10 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V70" t="n">
         <v>7</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7463,13 +7463,13 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U71" t="n">
         <v>8</v>
       </c>
       <c r="V71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W71" t="n">
         <v>18</v>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7519,12 +7519,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7565,10 +7565,10 @@
         <v>8</v>
       </c>
       <c r="U72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V72" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W72" t="n">
         <v>7</v>
@@ -7593,42 +7593,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_06.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
-        </is>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7661,16 +7661,16 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V73" t="n">
         <v>4</v>
       </c>
       <c r="W73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -7692,19 +7692,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_06.jpg</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_35.jpg</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
-        </is>
-      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_10.jpg</t>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7760,13 +7760,13 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
+      </c>
+      <c r="V74" t="n">
         <v>6</v>
-      </c>
-      <c r="U74" t="n">
-        <v>9</v>
-      </c>
-      <c r="V74" t="n">
-        <v>2</v>
       </c>
       <c r="W74" t="n">
         <v>8</v>
@@ -7791,14 +7791,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_08.jpg</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_21.jpg</t>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7859,10 +7859,10 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
         <v>9</v>
-      </c>
-      <c r="U75" t="n">
-        <v>5</v>
       </c>
       <c r="V75" t="n">
         <v>18</v>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,7 +7958,7 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U76" t="n">
         <v>7</v>
@@ -7967,7 +7967,7 @@
         <v>14</v>
       </c>
       <c r="W76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8066,7 +8066,7 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8165,7 +8165,7 @@
         <v>14</v>
       </c>
       <c r="W78" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>16</v>
       </c>
       <c r="V80" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W80" t="n">
         <v>11</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8456,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="U81" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V81" t="n">
         <v>8</v>
@@ -8484,17 +8484,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_45.jpg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8552,13 +8552,13 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
+        <v>6</v>
+      </c>
+      <c r="U82" t="n">
         <v>2</v>
       </c>
-      <c r="U82" t="n">
-        <v>9</v>
-      </c>
       <c r="V82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W82" t="n">
         <v>11</v>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8651,10 +8651,10 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V83" t="n">
         <v>7</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_34.jpg</t>
+          <t>stimuli/flower/flower_45.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8750,7 +8750,7 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U84" t="n">
         <v>1</v>
@@ -8759,7 +8759,7 @@
         <v>15</v>
       </c>
       <c r="W84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8858,7 +8858,7 @@
         <v>16</v>
       </c>
       <c r="W85" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8954,7 +8954,7 @@
         <v>8</v>
       </c>
       <c r="V86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W86" t="n">
         <v>4</v>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9050,7 +9050,7 @@
         <v>8</v>
       </c>
       <c r="U87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V87" t="n">
         <v>17</v>
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>stimuli/house/house_03.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_13.jpg</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_45.jpg</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_13.jpg</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V88" t="n">
         <v>16</v>
       </c>
       <c r="W88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_45.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9245,10 +9245,10 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V89" t="n">
         <v>4</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/jacket/jacket_48.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9344,7 +9344,7 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U90" t="n">
         <v>4</v>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_34.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9452,7 +9452,7 @@
         <v>15</v>
       </c>
       <c r="W91" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_48.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9548,7 +9548,7 @@
         <v>11</v>
       </c>
       <c r="V92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W92" t="n">
         <v>15</v>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W94" t="n">
         <v>18</v>
@@ -9776,12 +9776,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9842,10 +9842,10 @@
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W95" t="n">
         <v>4</v>
@@ -9870,12 +9870,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9938,10 +9938,10 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U96" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V96" t="n">
         <v>8</v>
@@ -9969,19 +9969,19 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_27.jpg</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_10.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_10.jpg</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_08.jpg</t>
@@ -9989,17 +9989,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10037,13 +10037,13 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U97" t="n">
         <v>8</v>
       </c>
       <c r="V97" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W97" t="n">
         <v>16</v>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10139,7 +10139,7 @@
         <v>8</v>
       </c>
       <c r="U98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V98" t="n">
         <v>7</v>
@@ -10167,17 +10167,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10187,17 +10187,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10235,13 +10235,13 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V99" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W99" t="n">
         <v>4</v>
@@ -10266,12 +10266,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10281,17 +10281,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U100" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V100" t="n">
         <v>14</v>
       </c>
       <c r="W100" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
@@ -10365,42 +10365,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_40.jpg</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_40.jpg</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
+        <v>2</v>
+      </c>
+      <c r="U101" t="n">
         <v>9</v>
-      </c>
-      <c r="U101" t="n">
-        <v>5</v>
       </c>
       <c r="V101" t="n">
         <v>17</v>
       </c>
       <c r="W101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10532,7 +10532,7 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U102" t="n">
         <v>7</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10640,7 +10640,7 @@
         <v>14</v>
       </c>
       <c r="W103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10739,7 +10739,7 @@
         <v>1</v>
       </c>
       <c r="W104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10835,7 +10835,7 @@
         <v>16</v>
       </c>
       <c r="V105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W105" t="n">
         <v>14</v>
